--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,22 +510,22 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion Oxford</t>
+          <t>Osney Bridge towpath closure Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards before bridge. Diversion via Abbey Road and Botley Road. Alternative continues via revised route.</t>
+          <t>Towpath closed approximately 150 yards before Osney Bridge. Diversion via Abbey Road and Botley Road. Related to Thames Water trunk main replacement and bridge structural work.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7527</v>
+        <v>51.753</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2731</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Henley footbridge closure</t>
+          <t>Marsh Lock footbridge closure Henley-Shiplake</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Closed for safety since May 2022. 3-mile diversion via A4155 pavements. No through access until further notice. Expected to remain until 31 January 2026, may be extended.</t>
+          <t>Footbridge closed south of Henley-on-Thames due to safety concerns. Diversion via A4155 pavements for approximately 3 miles (1.5 hours walk). Remains closed as of Jan 2025.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -580,17 +580,13 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -599,10 +595,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.4833</v>
+        <v>51.549</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.7333</v>
+        <v>-0.906</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -618,48 +614,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure</t>
+          <t>Swinford Bridge footpath closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed April 2025. Diversion via NCN 5.</t>
+          <t>Thames Path closed at Swinford Bridge from 20 February 2025 until 12 September 2026 for structural repairs. Diversion route available.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
+          <t>https://eynsham-pc.gov.uk/org-news.aspx?nid=3083</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.6833</v>
+        <v>51.797</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.2333</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -669,12 +665,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway intermittent closure</t>
+          <t>Abingdon Weir walkway closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Due to corrosion, walkway closed and re-routed via Abingdon town centre. Closes during high river levels and high flows, reopens when levels recede.</t>
+          <t>Walkway across weir closed due to corrosion. Path re-routed via Abingdon town centre. May reopen if river levels are low but closes again with rising water levels.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -682,13 +678,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -697,10 +693,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6702</v>
+        <v>51.67</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2693</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -711,7 +707,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -721,7 +717,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed since May 2023 for safety. Central span removed November 2025, beyond economical repair. Unlikely to reopen until 2028 at earliest.</t>
+          <t>Footbridge closed since May 2023 due to safety concerns and poor deck condition. Diversion via Temple Lane, Marlow Road, and Bisham Road. Rejoins at Causeway in Marlow.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -729,7 +725,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -739,19 +735,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
+          <t>https://gov.uk/government/news/temple-footbridge-closed-until-further-notice</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.552</v>
+        <v>51.547</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.797</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -767,12 +763,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 Runnymede closure Egham</t>
+          <t>Runnymede Bridge 142 footbridge closure Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Closed February 2024 due to structural damage from flooding. Diversion via A308/Runnymede Hotel area. Expected until at least 2026, possibly 2027.</t>
+          <t>Footbridge south of Runnymede Bridge/M25 closed since early 2024 due to structural damage from flooding. Diversion via A308 and A30 paths. Expected to last until at least 2026.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -780,17 +776,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -799,16 +795,16 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4375</v>
+        <v>51.423</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5347</v>
+        <v>-0.577</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -818,12 +814,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock refurbishment diversion</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Temporary diversion at Runnymede Pleasure Ground due to Bell Weir refurbishment works. Work started spring 2026, planned completion autumn 2027.</t>
+          <t>Small diversion at Runnymede Pleasure Grounds due to works on Bell Weir lock. Divert around compound with standing machinery, keeping it on left to return to river.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -834,39 +830,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4301</v>
+        <v>51.426</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5347</v>
+        <v>-0.574</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Streatley-Goring towpath diversion</t>
@@ -874,7 +866,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Half-mile diversion south of Goring Bridge due to eroding towpath. Funding insufficient for repairs. Unlikely to reopen until late 2026 at earliest.</t>
+          <t>Half mile (0.8km) diversion away from Thames due to eroding towpath south of Goring/Streatley Bridge. Riverside route unlikely to reopen until late 2026 at earliest.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -888,7 +880,7 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -897,31 +889,31 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.5229</v>
+        <v>51.609</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.1425</v>
+        <v>-1.301</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Penton Hook Island closure Staines</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed to public due to diseased trees (ash dieback). Thames Path unaffected. Complex clearance work ongoing.</t>
+          <t>Island remains closed to public since July 2025 due to diseased trees (ash dieback). Trees pose high risk from falling branches and collapsing trees. Specialist equipment needed for tree removal.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -929,7 +921,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -948,10 +940,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.4412</v>
+        <v>51.43</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.595</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -972,7 +964,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Closed March 2024 due to structural concerns. Between Rushey and Shifford locks near Buckland. Specialist survey completed but reopening date uncertain.</t>
+          <t>Bridge closed since March 2024 between Rushey and Shifford locks near Buckland village due to numerous structural and safety concerns.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -980,7 +972,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +982,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -999,21 +991,21 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.6942</v>
+        <v>51.693</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.4899</v>
+        <v>-1.489</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>incident</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1023,7 +1015,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank blocked between River Brent bridge and Brentford Marina. No official diversion. Area being redeveloped. Some sections now open.</t>
+          <t>Left bank path blocked on left bank of Grand Union Canal between bridge over River Brent and Brentford Marina. Divert via alternative route or Brentford High Street.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1031,13 +1023,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1046,10 +1038,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.4903</v>
+        <v>51.489</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.3027</v>
+        <v>-0.323</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,7 +510,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge towpath closure Oxford</t>
+          <t>Osney Bridge diversion, Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed approximately 150 yards before Osney Bridge. Diversion via Abbey Road and Botley Road. Related to Thames Water trunk main replacement and bridge structural work.</t>
+          <t>Towpath closed about 150 yards from Osney Bridge due to riverbank repairs. Diversion via Abbey Road and Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley-Shiplake</t>
+          <t>Marsh Lock footbridge closure, Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed south of Henley-on-Thames due to safety concerns. Diversion via A4155 pavements for approximately 3 miles (1.5 hours walk). Remains closed as of Jan 2025.</t>
+          <t>Footbridge closed for safety. Diversion via A4155 pavements, approximately 3 miles. Train/bus alternative available between Henley and Shiplake.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -583,10 +583,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -595,10 +599,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.549</v>
+        <v>51.542</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.906</v>
+        <v>-0.862</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -609,47 +613,43 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Swinford Bridge footpath closure</t>
+          <t>Sandford Footbridge closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Thames Path closed at Swinford Bridge from 20 February 2025 until 12 September 2026 for structural repairs. Diversion route available.</t>
+          <t>Unsafe footbridge closed north (upstream) of Sandford Lock. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://eynsham-pc.gov.uk/org-news.aspx?nid=3083</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.797</v>
+        <v>51.794</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.4</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -665,12 +665,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway closure</t>
+          <t>Abingdon Weir intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway across weir closed due to corrosion. Path re-routed via Abingdon town centre. May reopen if river levels are low but closes again with rising water levels.</t>
+          <t>Weir walkway closed due to corrosion. Rerouted via Abingdon town centre. May reopen if river levels are low but will close again when levels rise.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -684,7 +684,7 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.67</v>
+        <v>51.672</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.29</v>
+        <v>-1.295</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -712,42 +712,38 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Goring/Streatley towpath diversion</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed since May 2023 due to safety concerns and poor deck condition. Diversion via Temple Lane, Marlow Road, and Bisham Road. Rejoins at Causeway in Marlow.</t>
+          <t>Half mile diversion away from eroding Thames due to erosion south of Streatley/Goring Bridge. Riverside route unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>108.5</v>
+        <v>81.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://gov.uk/government/news/temple-footbridge-closed-until-further-notice</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.547</v>
+        <v>51.509</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.78</v>
+        <v>-1.304</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -763,48 +759,44 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Runnymede Bridge 142 footbridge closure Egham</t>
+          <t>Temple Footbridge closure near Marlow</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge south of Runnymede Bridge/M25 closed since early 2024 due to structural damage from flooding. Diversion via A308 and A30 paths. Expected to last until at least 2026.</t>
+          <t>Footbridge closed since May 2023 due to structural problems with deck boards. Diversion via Marlow Bridge and Bisham Road (via Temple Lane and Marlow Road).</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.5</v>
+        <v>108.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://gov.uk/government/news/temple-footbridge-closed-until-further-notice</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.423</v>
+        <v>51.552</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.577</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -814,16 +806,16 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Bridge 142 closure near Egham</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion at Runnymede Pleasure Grounds due to works on Bell Weir lock. Divert around compound with standing machinery, keeping it on left to return to river.</t>
+          <t>Footbridge closed due to structural damage from flooding. Diversion via A308 pavements and underpass, approx 0.6 miles. Expected closure until at least 2026, possibly 2027.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.2</v>
+        <v>136.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -833,25 +825,25 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.426</v>
+        <v>51.421</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.574</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -861,16 +853,16 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Bell Weir Lock diversion, Runnymede</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Half mile (0.8km) diversion away from Thames due to eroding towpath south of Goring/Streatley Bridge. Riverside route unlikely to reopen until late 2026 at earliest.</t>
+          <t>Small diversion at Runnymede Pleasure Ground around construction compound for Bell Weir refurbishment (spring 2026 to autumn 2027). Lock remains operational.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>136.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -880,19 +872,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.609</v>
+        <v>51.425</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.301</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -908,12 +900,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure Staines</t>
+          <t>Penton Hook Island closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island remains closed to public since July 2025 due to diseased trees (ash dieback). Trees pose high risk from falling branches and collapsing trees. Specialist equipment needed for tree removal.</t>
+          <t>Island closed to public due to diseased trees (ash dieback). Tree clearance work planned; unsafe for access. Thames Path itself unaffected.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -924,14 +916,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -940,10 +928,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.43</v>
+        <v>51.426</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.595</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -959,12 +947,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Ten Foot Bridge closure, Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed since March 2024 between Rushey and Shifford locks near Buckland village due to numerous structural and safety concerns.</t>
+          <t>Footbridge closed since March 2024 due to structural and safety concerns. Located between Rushey and Shifford locks near Buckland.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -982,7 +970,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -991,10 +979,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.693</v>
+        <v>51.694</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.489</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -1005,7 +993,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1015,7 +1003,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank path blocked on left bank of Grand Union Canal between bridge over River Brent and Brentford Marina. Divert via alternative route or Brentford High Street.</t>
+          <t>Path blocked on left bank of Grand Union Canal between bridge over River Brent and Brentford Marina. Alternative via The Ham, canal walk to Thames Lock, then Dock Road.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1023,13 +1011,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1038,10 +1026,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.489</v>
+        <v>51.492</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.323</v>
+        <v>-0.307</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,22 +510,22 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion, Oxford</t>
+          <t>Osney Bridge diversion Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards from Osney Bridge due to riverbank repairs. Diversion via Abbey Road and Botley Road.</t>
+          <t>Towpath closed 150 yards upstream of Osney Bridge. Diversion via Abbey Road and Botley Road. Repairs to riverbank.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.753</v>
+        <v>51.7527</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.273</v>
+        <v>-1.2731</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,12 +567,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure, Henley</t>
+          <t>Marsh Lock footbridge closure Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. Diversion via A4155 pavements, approximately 3 miles. Train/bus alternative available between Henley and Shiplake.</t>
+          <t>Unsafe footbridge closed by Environment Agency. 3-mile diversion via A4155 and Harpsden. Closure order until 31 Jan 2026, may be extended.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -585,12 +585,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.542</v>
+        <v>51.5667</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.862</v>
+        <v>-0.9167</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed north (upstream) of Sandford Lock. Diversion via NCN 5.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5 cycle route.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -634,10 +634,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -646,16 +650,16 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.794</v>
+        <v>51.625</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.188</v>
+        <v>-1.175</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -670,7 +674,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weir walkway closed due to corrosion. Rerouted via Abingdon town centre. May reopen if river levels are low but will close again when levels rise.</t>
+          <t>Walkway closed intermittently due to corrosion concerns and high river flows. Closed late Sept 2025. Reopened 30 Sept with trigger-based closures.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -678,25 +682,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
+          <t>intermittent</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/abingdon-weir-walkway</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.672</v>
+        <v>51.6689</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.295</v>
+        <v>-1.2692</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -712,38 +720,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Goring/Streatley towpath diversion</t>
+          <t>Temple Footbridge closure Hurley</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Half mile diversion away from eroding Thames due to erosion south of Streatley/Goring Bridge. Riverside route unlikely to reopen until late 2026.</t>
+          <t>Structural safety concerns. Closed 15 May 2023. Central span removed Nov 2025. Remains closed indefinitely. Diversion via Bisham and Marlow.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>81.5</v>
+        <v>108.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.509</v>
+        <v>51.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-1.304</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -759,44 +771,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure near Marlow</t>
+          <t>Bridge 142 closure Runnymede Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed since May 2023 due to structural problems with deck boards. Diversion via Marlow Bridge and Bisham Road (via Temple Lane and Marlow Road).</t>
+          <t>Structural damage to footbridge. Closed Feb 2024. Diversion via A308 and roundabout. Expected to last until at least 2026/2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>108.5</v>
+        <v>136.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://gov.uk/government/news/temple-footbridge-closed-until-further-notice</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.552</v>
+        <v>51.4447</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.797</v>
+        <v>-0.5167</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -806,16 +822,16 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure near Egham</t>
+          <t>Bell Weir Lock diversion Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed due to structural damage from flooding. Diversion via A308 pavements and underpass, approx 0.6 miles. Expected closure until at least 2026, possibly 2027.</t>
+          <t>Small diversion at Runnymede Pleasure Ground. Temporary towpath diversion for £22m weir refurbishment works.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.5</v>
+        <v>136.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -825,44 +841,44 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.421</v>
+        <v>51.441</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.518</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion, Runnymede</t>
+          <t>Streatley-Goring towpath diversion</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Small diversion at Runnymede Pleasure Ground around construction compound for Bell Weir refurbishment (spring 2026 to autumn 2027). Lock remains operational.</t>
+          <t>Half-mile diversion due to eroding towpath. Riverside route unlikely to reopen until late 2026. Insufficient funding for repairs.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>136.2</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -872,19 +888,19 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.425</v>
+        <v>51.5283</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.588</v>
+        <v>-1.1817</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -905,7 +921,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed to public due to diseased trees (ash dieback). Tree clearance work planned; unsafe for access. Thames Path itself unaffected.</t>
+          <t>Island closed to public due to diseased and dangerous trees. Thames Path unaffected. No access to island until tree management completed.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -913,13 +929,13 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -928,10 +944,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.426</v>
+        <v>51.436</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.576</v>
+        <v>-0.496</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -947,12 +963,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure, Faringdon</t>
+          <t>Ten Foot Bridge closure Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed since March 2024 due to structural and safety concerns. Located between Rushey and Shifford locks near Buckland.</t>
+          <t>Closed March 2024 due to structural and safety concerns. Specialist survey completed. Status unclear for reopening.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -960,7 +976,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -970,7 +986,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1003,7 +1019,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path blocked on left bank of Grand Union Canal between bridge over River Brent and Brentford Marina. Alternative via The Ham, canal walk to Thames Lock, then Dock Road.</t>
+          <t>Left bank path blocked between River Brent and Brentford Marina. Redevelopment ongoing. Alternative: Brentford High Street or use right bank/Thames Lock route.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1011,13 +1027,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>partial access</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1026,10 +1042,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.492</v>
+        <v>51.491</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.307</v>
+        <v>-0.305</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -520,38 +520,42 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge diversion Oxford</t>
+          <t>Marsh Lock Bridge - Henley</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed 150 yards upstream of Osney Bridge. Diversion via Abbey Road and Botley Road. Repairs to riverbank.</t>
+          <t>Footbridge closed due to safety concerns. Diversion of 3 miles via A4155 and Harpsden.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53.8</v>
+        <v>105.1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7527</v>
+        <v>51.494</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2731</v>
+        <v>-0.778</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -567,16 +571,16 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley</t>
+          <t>Sandford Footbridge - Oxford</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed by Environment Agency. 3-mile diversion via A4155 and Harpsden. Closure order until 31 Jan 2026, may be extended.</t>
+          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>105.1</v>
+        <v>57</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -585,75 +589,75 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.5667</v>
+        <v>51.744</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.9167</v>
+        <v>-1.183</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure</t>
+          <t>Abingdon Weir Walkway - Intermittent</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5 cycle route.</t>
+          <t>Closed intermittently due to high river levels and corrosion. Reopened 30 Sept 2025 with trigger-based closures.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/abingdon-weir-walkway</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.625</v>
+        <v>51.667</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.175</v>
+        <v>-1.283</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -664,47 +668,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir intermittent closure</t>
+          <t>Temple Footbridge - Hurley</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walkway closed intermittently due to corrosion concerns and high river flows. Closed late Sept 2025. Reopened 30 Sept with trigger-based closures.</t>
+          <t>Closed May 2023 for structural safety. Central section removed Nov 2025, beyond repair.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>62</v>
+        <v>108.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/abingdon-weir-walkway</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6689</v>
+        <v>51.552</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2692</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -720,48 +724,48 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closure Hurley</t>
+          <t>Bridge 142 - Runnymede</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Structural safety concerns. Closed 15 May 2023. Central span removed Nov 2025. Remains closed indefinitely. Diversion via Bisham and Marlow.</t>
+          <t>Closed February 2024 after tree strike. Diversion via A308. Repairs possible 2027.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>108.5</v>
+        <v>136.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.552</v>
+        <v>51.428</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.797</v>
+        <v>-0.534</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,48 +775,44 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 closure Runnymede Egham</t>
+          <t>Bell Weir Lock - Diversion</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Structural damage to footbridge. Closed Feb 2024. Diversion via A308 and roundabout. Expected to last until at least 2026/2027.</t>
+          <t>Small diversion around compound at Runnymede Pleasure Grounds for works.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.5</v>
+        <v>136.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temporary-diversion-near-runnymede-bridge/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.4447</v>
+        <v>51.426</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5167</v>
+        <v>-0.533</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -822,16 +822,16 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock diversion Runnymede</t>
+          <t>Streatley-Goring Towpath - Eroding</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Small diversion at Runnymede Pleasure Ground. Temporary towpath diversion for £22m weir refurbishment works.</t>
+          <t>0.5 mile diversion due to eroding towpath. Repairs unlikely until late 2026.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.2</v>
+        <v>81.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -841,19 +841,19 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.441</v>
+        <v>51.523</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.518</v>
+        <v>-1.143</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -864,176 +864,172 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath diversion</t>
+          <t>Penton Hook Island - Tree Safety</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Half-mile diversion due to eroding towpath. Riverside route unlikely to reopen until late 2026. Insufficient funding for repairs.</t>
+          <t>Closed since February 2025 due to Ash Dieback disease. Tree clearance ongoing.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>135.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.5283</v>
+        <v>51.434</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.1817</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>closure</t>
-        </is>
-      </c>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island closure</t>
+          <t>Ten Foot Bridge - Faringdon</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed to public due to diseased and dangerous trees. Thames Path unaffected. No access to island until tree management completed.</t>
+          <t>Thames Path does not cross this bridge. No closure currently reported.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>135.6</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://en.wikipedia.org/wiki/Tenfoot_Bridge</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.436</v>
+        <v>51.694</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.496</v>
+        <v>-1.489</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge closure Faringdon</t>
+          <t>Brentford Grand Union Canal - Redevelopment</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Closed March 2024 due to structural and safety concerns. Specialist survey completed. Status unclear for reopening.</t>
+          <t>Left bank blocked between River Brent bridge and Marina. Partial reopening via The Ham to Thames Lock.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/ten-foot-bridge-2</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.694</v>
+        <v>51.491</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.49</v>
+        <v>-0.298</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Osney Bridge Diversion - Oxford</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank path blocked between River Brent and Brentford Marina. Redevelopment ongoing. Alternative: Brentford High Street or use right bank/Thames Lock route.</t>
+          <t>Short riverbank repair diversion via Abbey Road and Botley Road.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>154</v>
+        <v>53.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>partial access</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1042,10 +1038,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.491</v>
+        <v>51.753</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.305</v>
+        <v>-1.273</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -510,7 +510,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -520,16 +520,16 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Bridge - Henley</t>
+          <t>Osney Bridge Oxford water main/footpath works</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed due to safety concerns. Diversion of 3 miles via A4155 and Harpsden.</t>
+          <t>Thames towpath diversion via Abbey Road. Water mains replacement and footpath repairs. Phase 2 main works Nov 2024-Aug 2026. Phase 3 decommission July-Oct 2026.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>105.1</v>
+        <v>53.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -538,24 +538,24 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
+          <t>https://www.thameswater.co.uk/about-us/projects/improvements-in-your-area/osney-bridge-trunk-main-replacement</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.494</v>
+        <v>51.752694</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.778</v>
+        <v>-1.273093</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -571,16 +571,16 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge - Oxford</t>
+          <t>Marsh Lock Henley footbridge closure</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge north of Sandford Lock closed. Diversion via NCN 5.</t>
+          <t>Footbridge closed for safety. 3-mile diversion via Shiplake. Closure order valid until 31 Jan 2026 and may be extended. Repairs in design phase, expected late 2026 at earliest.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>57</v>
+        <v>105.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -589,75 +589,75 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.744</v>
+        <v>51.48</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-1.183</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir Walkway - Intermittent</t>
+          <t>Sandford Footbridge closure near Oxford</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Closed intermittently due to high river levels and corrosion. Reopened 30 Sept 2025 with trigger-based closures.</t>
+          <t>Unsafe footbridge closed north (upstream) of Sandford Lock. Diversion via NCN 5 cycle route. Environment Agency closure due to safety concerns.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/abingdon-weir-walkway</t>
+          <t>https://nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.667</v>
+        <v>51.51</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.283</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -668,47 +668,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge - Hurley</t>
+          <t>Abingdon Weir walkway intermittent closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Closed May 2023 for structural safety. Central section removed Nov 2025, beyond repair.</t>
+          <t>Weir walkway closes when river levels high and radial gates operated. Reopened 1 April 2026 with 1.5m width. Closed intermittently due to high flows and trigger points during gate operations.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>108.5</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.552</v>
+        <v>51.45</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.797</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -724,16 +724,16 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 - Runnymede</t>
+          <t>Temple Footbridge closed Hurley near Marlow</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Closed February 2024 after tree strike. Diversion via A308. Repairs possible 2027.</t>
+          <t>Wooden footbridge closed May 2023 for safety. Unlikely to reopen before 2028. Central span removed Nov 2025. DEFRA offered £250k. Diversion via Marlow Bridge adding 0.5 miles.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>136.5</v>
+        <v>108.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -742,30 +742,30 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.428</v>
+        <v>51.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.534</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -775,44 +775,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock - Diversion</t>
+          <t>Bridge 142 Egham Runnymede footbridge closure</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Small diversion around compound at Runnymede Pleasure Grounds for works.</t>
+          <t>90-year-old bridge closed Feb 2024 after tree strike. Significant structural damage with cracks in cast iron. Diversion via A308/Causeway/Runnymede Roundabout. Funding for repairs available 2025-26, repairs estimated 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.2</v>
+        <v>136.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.426</v>
+        <v>51.43</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.533</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -822,16 +826,16 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring Towpath - Eroding</t>
+          <t>Bell Weir Lock Runnymede diversion for weir works</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0.5 mile diversion due to eroding towpath. Repairs unlikely until late 2026.</t>
+          <t>Thames Path diverted around compound at Runnymede Pleasure Grounds during Bell Weir weir refurbishment works. Lock remains operational. Small diversion around machinery compound.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>81.5</v>
+        <v>136.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -841,166 +845,174 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.523</v>
+        <v>51.4</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-1.143</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island - Tree Safety</t>
+          <t>Streatley-Goring towpath closure eroding bank</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Closed since February 2025 due to Ash Dieback disease. Tree clearance ongoing.</t>
+          <t>0.8km diversion away from river due to eroding towpath. Repairs expected late 2026 at earliest. Insufficient funding secured. Footpath narrow and frequently floods.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.6</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.434</v>
+        <v>51.522</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.519</v>
+        <v>-1.143</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>closure</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge - Faringdon</t>
+          <t>Penton Hook Island tree safety closure</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Thames Path does not cross this bridge. No closure currently reported.</t>
+          <t>Island closed to public since Feb 2025 due to diseased trees (ash dieback). Scale/complexity of clearing work requires specialist equipment brought by river. Thames Path unaffected. Island remains closed indefinitely.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34</v>
+        <v>135.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tenfoot_Bridge</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.694</v>
+        <v>51.38</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.489</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal - Redevelopment</t>
+          <t>Ten Foot Bridge Faringdon reconstruction completed</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Left bank blocked between River Brent bridge and Marina. Partial reopening via The Ham to Thames Lock.</t>
+          <t>Bridge reconstruction completed 18 Aug 2026. Pedestrian crossing between Rushey and Shifford Locks near Buckland in Faringdon fully restored. Previously closed for reconstruction works.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+          <t>reopened</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.491</v>
+        <v>51.694</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.298</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1010,26 +1022,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge Diversion - Oxford</t>
+          <t>Brentford Grand Union Canal/Thames junction disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Short riverbank repair diversion via Abbey Road and Botley Road.</t>
+          <t>Left bank path blocked at Grand Union Canal junction. Being redeveloped. Parts of route now open. Walk down The Ham, cross canal, follow canal to Thames Lock, cross back at lock, follow Dock Road to High Street.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>53.8</v>
+        <v>154</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1038,10 +1050,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.753</v>
+        <v>51.49</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-1.273</v>
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,42 +520,38 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge Oxford water main/footpath works</t>
+          <t>Osney Bridge towpath diversion</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thames towpath diversion via Abbey Road. Water mains replacement and footpath repairs. Phase 2 main works Nov 2024-Aug 2026. Phase 3 decommission July-Oct 2026.</t>
+          <t>Towpath closed about 150 yards before bridge, diversion via Abbey Road and Botley Road</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53.8</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.thameswater.co.uk/about-us/projects/improvements-in-your-area/osney-bridge-trunk-main-replacement</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.752694</v>
+        <v>51.7467</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.273093</v>
+        <v>-1.2742</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -566,47 +562,43 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock Henley footbridge closure</t>
+          <t>Donnington Bridge Oxford short diversion</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed for safety. 3-mile diversion via Shiplake. Closure order valid until 31 Jan 2026 and may be extended. Repairs in design phase, expected late 2026 at earliest.</t>
+          <t>Short diversion for riverbank repairs, about 400m, no additional distance</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>105.1</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.48</v>
+        <v>51.7356</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.82</v>
+        <v>-1.2356</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -617,17 +609,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge closure near Oxford</t>
+          <t>Sandford Footbridge unsafe closure</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed north (upstream) of Sandford Lock. Diversion via NCN 5 cycle route. Environment Agency closure due to safety concerns.</t>
+          <t>Unsafe footbridge closed north of Sandford Lock, diversion via NCN 5</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -638,26 +630,22 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.51</v>
+        <v>51.7201</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-1.19</v>
+        <v>-1.2018</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -673,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway intermittent closure</t>
+          <t>Abingdon Weir walkway corrosion closure</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weir walkway closes when river levels high and radial gates operated. Reopened 1 April 2026 with 1.5m width. Closed intermittently due to high flows and trigger points during gate operations.</t>
+          <t>Weir walkway closed due to corrosion, rerouted via Abingdon town centre. May reopen in low water</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -686,29 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets</t>
+          <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.45</v>
+        <v>51.6701</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.2845</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -719,47 +703,43 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge closed Hurley near Marlow</t>
+          <t>Goring-Streatley towpath erosion diversion</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Wooden footbridge closed May 2023 for safety. Unlikely to reopen before 2028. Central span removed Nov 2025. DEFRA offered £250k. Diversion via Marlow Bridge adding 0.5 miles.</t>
+          <t>Half-mile diversion away from Thames due to eroding towpath, riverside unlikely to reopen until late 2026</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>108.5</v>
+        <v>81.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.552</v>
+        <v>51.5226</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.797</v>
+        <v>-1.2847</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -770,21 +750,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 Egham Runnymede footbridge closure</t>
+          <t>Marsh Lock footbridge closure Henley-Shiplake</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90-year-old bridge closed Feb 2024 after tree strike. Significant structural damage with cracks in cast iron. Diversion via A308/Causeway/Runnymede Roundabout. Funding for repairs available 2025-26, repairs estimated 2027.</t>
+          <t>Footbridge closed south of Henley-on-Thames due to safety concerns, 3-mile diversion in place</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.5</v>
+        <v>105</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -793,49 +773,49 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.43</v>
+        <v>51.533</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.9078000000000001</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock Runnymede diversion for weir works</t>
+          <t>Temple Footbridge long-term closure</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thames Path diverted around compound at Runnymede Pleasure Grounds during Bell Weir weir refurbishment works. Lock remains operational. Small diversion around machinery compound.</t>
+          <t>Bridge closed for foreseeable future due to structural safety concerns, diversion in place</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.2</v>
+        <v>108.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -845,44 +825,44 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.4</v>
+        <v>51.5071</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.8547</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Streatley-Goring towpath closure eroding bank</t>
+          <t>Bridge 142 Runnymede structural damage closure</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0.8km diversion away from river due to eroding towpath. Repairs expected late 2026 at earliest. Insufficient funding secured. Footpath narrow and frequently floods.</t>
+          <t>Bridge closed due to structural damage from tree strike, diversion via A308, may extend to 2027</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>81.5</v>
+        <v>136.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -892,76 +872,72 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-diversion-streatley-goring/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131327/faqs</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.522</v>
+        <v>51.4316</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-1.143</v>
+        <v>-0.5485</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island tree safety closure</t>
+          <t>Bell Weir Lock refurbishment diversion</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Island closed to public since Feb 2025 due to diseased trees (ash dieback). Scale/complexity of clearing work requires specialist equipment brought by river. Thames Path unaffected. Island remains closed indefinitely.</t>
+          <t>Thames Towpath temporarily diverted during Bell Weir weir refurbishment, spring 2026 to autumn 2027</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>135.6</v>
+        <v>136.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.38</v>
+        <v>51.4301</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.5461</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -971,63 +947,59 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ten Foot Bridge Faringdon reconstruction completed</t>
+          <t>Penton Hook Island diseased tree closure</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bridge reconstruction completed 18 Aug 2026. Pedestrian crossing between Rushey and Shifford Locks near Buckland in Faringdon fully restored. Previously closed for reconstruction works.</t>
+          <t>Island access closed due to diseased and dangerous trees, Thames Path itself unaffected</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34</v>
+        <v>135.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>reopened</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.694</v>
+        <v>51.4278</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.49</v>
+        <v>-0.5181</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>info</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>diversion</t>
+          <t>closure</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal/Thames junction disruption</t>
+          <t>Brentford Grand Union Canal disruption</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank path blocked at Grand Union Canal junction. Being redeveloped. Parts of route now open. Walk down The Ham, cross canal, follow canal to Thames Lock, cross back at lock, follow Dock Road to High Street.</t>
+          <t>Left bank blocked between River Brent bridge and Brentford Marina, area being redeveloped</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1035,13 +1007,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1050,10 +1022,108 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51.49</v>
+        <v>51.4817</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.3042</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Ten Foot Bridge Faringdon - status unclear</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Bridge mentioned in closure tracking but Thames Path does not cross it</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>51.6896</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>-1.4899</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>diversion</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Isis Farmhouse to Donnington Bridge closure</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Thames path closed between Isis Farmhouse and Donnington Bridge for towpath bank repairs, expected November reopening</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thamespath.org.uk/</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>51.7412</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>-1.2591</v>
       </c>
     </row>
   </sheetData>

--- a/PathStatus.xlsx
+++ b/PathStatus.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -510,26 +510,26 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>diversion</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Osney Bridge towpath diversion</t>
+          <t>Osney Bridge Oxford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towpath closed about 150 yards before bridge, diversion via Abbey Road and Botley Road</t>
+          <t>Towpath closure upstream of bridge. Diversion via Abbey Road and Botley Road.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>53</v>
+        <v>53.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.7467</v>
+        <v>51.75252</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.2742</v>
+        <v>-1.2726</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -562,43 +562,47 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Donnington Bridge Oxford short diversion</t>
+          <t>Marsh Lock Footbridge Henley</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Short diversion for riverbank repairs, about 400m, no additional distance</t>
+          <t>Footbridge closed for safety. 3-mile diversion via Shiplake. Closure until 31 Jan 2026, may extend.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55</v>
+        <v>105.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.7356</v>
+        <v>51.52803</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-1.2356</v>
+        <v>-0.8871</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -609,17 +613,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>intermittent</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sandford Footbridge unsafe closure</t>
+          <t>Sandford Footbridge</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unsafe footbridge closed north of Sandford Lock, diversion via NCN 5</t>
+          <t>Unsafe tributary bridge closed. Diversion via NCN Route 5 cycle path alongside railway.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -633,20 +637,16 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>51.7201</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>-1.2018</v>
-      </c>
+          <t>https://nationaltrail.co.uk/en_GB/short-routes/sandford-footbridge-closure-and-diversion-april-2025/</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Abingdon Weir walkway corrosion closure</t>
+          <t>Abingdon Weir Walkway</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weir walkway closed due to corrosion, rerouted via Abingdon town centre. May reopen in low water</t>
+          <t>Corrosion concerns. Reopened 30 Sept 2025. Closed intermittently during high flows/gate operation.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -674,25 +674,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://walkthethames.co.uk/thames-path-status/</t>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/159321/faqs</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.6701</v>
+        <v>51.670535</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-1.2845</v>
+        <v>-1.269202</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -703,21 +703,21 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Goring-Streatley towpath erosion diversion</t>
+          <t>Temple Footbridge Hurley</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Half-mile diversion away from Thames due to eroding towpath, riverside unlikely to reopen until late 2026</t>
+          <t>Closed May 2023 for safety. Central section removed Nov 2025. Bridge requires complete replacement. Diversion via Bisham/Marlow until 2028 at earliest.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>81.5</v>
+        <v>108.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
+          <t>https://www.thamespath.org.uk/2025/12/04/temple-bridge-closed-until-2028-at-least/</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.5226</v>
+        <v>51.552</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-1.2847</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -750,72 +750,66 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Marsh Lock footbridge closure Henley-Shiplake</t>
+          <t>Bridge 142 Runnymede Egham</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Footbridge closed south of Henley-on-Thames due to safety concerns, 3-mile diversion in place</t>
+          <t>Cast iron pedestrian bridge damaged. Closed Feb 2024. Diversion via A308. Expected closure until 2027.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>105</v>
+        <v>136.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/thames-path-marsh-lock-footbridge-closure-and-diversion/</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>51.533</v>
-      </c>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/news_feed/bridge-142-river-thames-egham</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.53472</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Temple Footbridge long-term closure</t>
+          <t>Bell Weir Lock Works Runnymede</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed for foreseeable future due to structural safety concerns, diversion in place</t>
+          <t>Lock remains operational. Temporary diversion at Runnymede Pleasure Grounds. Refurbishment work ongoing.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>108.5</v>
+        <v>136.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -825,19 +819,17 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.nationaltrail.co.uk/en_GB/short-routes/temple-bridge-closed-thames-path-on-diversion-may-2023-onwards/</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>51.5071</v>
-      </c>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n">
-        <v>-0.8547</v>
+        <v>-0.53472</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -853,16 +845,16 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Bridge 142 Runnymede structural damage closure</t>
+          <t>Streatley-Goring Towpath</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed due to structural damage from tree strike, diversion via A308, may extend to 2027</t>
+          <t>Eroding towpath closure. 0.5-mile diversion inland via Manor Road. Unlikely to reopen until late 2026.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>136.5</v>
+        <v>81.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -872,44 +864,40 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/131327/faqs</t>
+          <t>https://www.thamespath.org.uk/2025/12/02/goring-diversion-continues-into-2026/</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.4316</v>
+        <v>51.522917</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.5485</v>
+        <v>-1.1425</v>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
+          <t>closure</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bell Weir Lock refurbishment diversion</t>
+          <t>Penton Hook Island</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Thames Towpath temporarily diverted during Bell Weir weir refurbishment, spring 2026 to autumn 2027</t>
+          <t>Island closed to public. Diseased trees (ash dieback) pose safety risk. Thames Path unaffected.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>136.2</v>
+        <v>135.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -919,20 +907,16 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/141856/faqs</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>51.4301</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.5461</v>
-      </c>
+          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -942,64 +926,64 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Penton Hook Island diseased tree closure</t>
+          <t>Ten Foot Bridge Faringdon</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Island access closed due to diseased and dangerous trees, Thames Path itself unaffected</t>
+          <t>Footbridge open to public. Thames Path passes north bank but does not cross.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>135.6</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets/widgets/129061/faqs</t>
+          <t>https://en.wikipedia.org/wiki/Tenfoot_Bridge</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.4278</v>
+        <v>51.694223</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.5181</v>
+        <v>-1.489891</v>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>closure</t>
+          <t>diversion</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Brentford Grand Union Canal disruption</t>
+          <t>Brentford Grand Union Canal</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Left bank blocked between River Brent bridge and Brentford Marina, area being redeveloped</t>
+          <t>Left bank path blocked between River Brent bridge and Brentford Marina. Redevelopment ongoing. No official diversion.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1013,7 +997,7 @@
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1021,110 +1005,8 @@
           <t>https://walkthethames.co.uk/thames-path-status/</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>51.4817</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>-0.3042</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Ten Foot Bridge Faringdon - status unclear</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Bridge mentioned in closure tracking but Thames Path does not cross it</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://engageenvironmentagency.uk.engagementhq.com/thames-area-assets</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>51.6896</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>-1.4899</v>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>diversion</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Isis Farmhouse to Donnington Bridge closure</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Thames path closed between Isis Farmhouse and Donnington Bridge for towpath bank repairs, expected November reopening</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thamespath.org.uk/</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>51.7412</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>-1.2591</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
